--- a/backend/templates/Hikma orders.xlsx
+++ b/backend/templates/Hikma orders.xlsx
@@ -793,10 +793,10 @@
         <v>9</v>
       </c>
       <c r="B7" s="12">
-        <v>6187</v>
+        <v>4125</v>
       </c>
       <c r="C7" s="12">
-        <v>6583</v>
+        <v>4389</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="10"/>
